--- a/sports_forms/007_online_training_enquiry_form--sports_forms.xlsx
+++ b/sports_forms/007_online_training_enquiry_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>golf</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Hockey</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hockey</t>
+          <t>Soccer</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>soccer</t>
+          <t>tabletennis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Soccer</t>
+          <t>TableTennis</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tabletennis</t>
+          <t>running</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TableTennis</t>
+          <t>Running</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Running</t>
+          <t>Baseball</t>
         </is>
       </c>
     </row>
@@ -1488,775 +1488,61 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>baseball</t>
+          <t>softball</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baseball</t>
+          <t>Softball</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sport_interests_choices</t>
+          <t>contact_preference_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>softball</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Softball</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sport_interests_choices</t>
+          <t>contact_preference_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sport_interests_choices</t>
+          <t>contact_preference_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cricket</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
-        <is>
-          <t>Cricket</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Rugby</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Hockey</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>golf</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Golf</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Football</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Basketball</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Volleyball</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>cycling</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Cycling</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>badminton</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Badminton</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>swimming</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Swimming</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>boxing</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Boxing</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>wrestling</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Wrestling</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>tabletennis</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>TableTennis</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>baseball</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Baseball</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>softball</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Softball</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>golf</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Golf</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Hockey</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>golf</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Golf</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>tennis</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tennis</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>cricket</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Cricket</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Rugby</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>golf</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Golf</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>baseball</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Baseball</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>softball</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Softball</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>tennis</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Tennis</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>cricket</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Cricket</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Rugby</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Hockey</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>golf</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Golf</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Football</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Basketball</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Volleyball</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>cycling</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Cycling</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>badminton</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Badminton</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>swimming</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Swimming</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>boxing</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Boxing</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>wrestling</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Wrestling</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>tabletennis</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>TableTennis</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>sport_interests_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Running</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>contact_preference_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>contact_preference_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>contact_preference_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>sms</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
         <is>
           <t>SMS</t>
         </is>
